--- a/data/AttributePool.xlsx
+++ b/data/AttributePool.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,12 @@
           <t>desc</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>owner_type</t>
+        </is>
+      </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -510,6 +512,11 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>说明</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>归属(0=角色,1=宝宝)</t>
         </is>
       </c>
     </row>
@@ -545,6 +552,9 @@
           <t>每升一级获得 5 点,分配到体质/灵力/力量/敏捷</t>
         </is>
       </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -578,6 +588,9 @@
           <t>每升一级获得 1 点,五行相性单项上限 50</t>
         </is>
       </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -610,6 +623,45 @@
         <is>
           <t>60 级解锁,每级 1 点,仙/魔两路强化</t>
         </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>宝宝属性点</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>宝宝每升一级获得 5 点,分配到体质/灵力/力量/敏捷</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
